--- a/plot/data/source_data/source_data_fig_4_d.xlsx
+++ b/plot/data/source_data/source_data_fig_4_d.xlsx
@@ -19616,19 +19616,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-0.3229788835169755</v>
+        <v>-0.3229789946627743</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.1804221946434055</v>
+        <v>0.180421905914194</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.7239891423109344</v>
+        <v>0.7239890618425874</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.5083424791349364</v>
+        <v>0.5083427103052852</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1.031116421897505</v>
+        <v>1.031115723785879</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -19653,19 +19653,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>-0.7146395169760119</v>
+        <v>-0.7146373228793279</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.2545824912924451</v>
+        <v>0.2545825366005259</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.4893684890366935</v>
+        <v>0.4893695627596505</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.2971221245267348</v>
+        <v>0.2971227500569612</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.8060036540311828</v>
+        <v>0.8060054940581307</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -19690,19 +19690,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.3134863385562937</v>
+        <v>0.3134883621164159</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.2007694534845734</v>
+        <v>0.2007692477496069</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1.368186771227573</v>
+        <v>1.368189539838564</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.923102906400407</v>
+        <v>0.9231051465830248</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>2.027872545934934</v>
+        <v>2.02787583175423</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -19727,19 +19727,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.3761607258499093</v>
+        <v>0.3761623010304273</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.2453113790961737</v>
+        <v>0.2453112405821313</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1.45668124128757</v>
+        <v>1.45668353582529</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9006480293224285</v>
+        <v>0.900649692517403</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2.355992762583903</v>
+        <v>2.35599583408892</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -19764,19 +19764,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.7429468047084797</v>
+        <v>0.7429464622158767</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.3461391198006431</v>
+        <v>0.3461391158059813</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2.102120936276155</v>
+        <v>2.102120216315407</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1.066653946871844</v>
+        <v>1.06665358990207</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>4.142779805662183</v>
+        <v>4.142778354355546</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -19801,19 +19801,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-0.5496529964038792</v>
+        <v>-0.5496516536904712</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.2981243567917803</v>
+        <v>0.2981242194522927</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.5771500487791829</v>
+        <v>0.5771508237268121</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.3217546441331075</v>
+        <v>0.32175516276786</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1.035267663978181</v>
+        <v>1.035268775372736</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -19838,19 +19838,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-1.054180440002632</v>
+        <v>-1.054179101067505</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.3833028160783373</v>
+        <v>0.3833020641690884</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.3484779088596553</v>
+        <v>0.3484783754492811</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.164402078303866</v>
+        <v>0.1644025407100506</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.7386576509011356</v>
+        <v>0.7386575513449236</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
